--- a/tools/importer/reports/import-content-page.report.xlsx
+++ b/tools/importer/reports/import-content-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>baggage-allowance.report.json</t>
   </si>
   <si>
-    <t>["accordion-faq","accordion-faq"]</t>
+    <t>["accordion-faq","accordion-faq","table"]</t>
   </si>
   <si>
     <t>baggage-allowance</t>
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-07-14T13:20:57.669Z</t>
+    <t>2026-07-19T09:48:26.006Z</t>
   </si>
   <si>
     <t>Nile Air – Your Journey, Our Care</t>
@@ -73,7 +73,7 @@
     <t>home-landing</t>
   </si>
   <si>
-    <t>2026-07-14T13:20:21.042Z</t>
+    <t>2026-07-19T09:47:55.705Z</t>
   </si>
   <si>
     <t>https://www.nileair.com/</t>
@@ -88,7 +88,7 @@
     <t>nileair-holidays</t>
   </si>
   <si>
-    <t>2026-07-14T13:21:09.399Z</t>
+    <t>2026-07-19T09:48:39.465Z</t>
   </si>
   <si>
     <t>https://www.nileair.com/nileair-holidays</t>
@@ -103,7 +103,7 @@
     <t>travelling-pets</t>
   </si>
   <si>
-    <t>2026-07-14T13:20:48.067Z</t>
+    <t>2026-07-19T09:48:13.626Z</t>
   </si>
   <si>
     <t>https://www.nileair.com/travelling-pets</t>
